--- a/apps/api/test/fixtures/capex-plan-synthetic-changed.xlsx
+++ b/apps/api/test/fixtures/capex-plan-synthetic-changed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="171">
   <si>
     <t>MASTER_FILE - ΑΝΑΠΤΥΞΙΑΚΟΣ ΠΡΟΫΠΟΛΟΓΙΣΜΟΣ - Αναθεώρηση Budget 2026 (συνθετικό αρχείο δοκιμών)</t>
   </si>
@@ -506,9 +506,6 @@
   </si>
   <si>
     <t>ΠΡΩΤΟΒΑΘΜΙΑ ΦΡΟΝΤΙΔΑ ΥΓΕΙΑΣ</t>
-  </si>
-  <si>
-    <t>ΥΠΗΡΕΣΙΑ ΑΣΘΕΝΟΦΟΡΩΝ</t>
   </si>
   <si>
     <t>Ανακαίνιση αποδυτηρίων προσωπικού δεύτερου ορόφου</t>
@@ -9255,13 +9252,13 @@
         <v>110</v>
       </c>
       <c r="C115" t="s">
+        <v>83</v>
+      </c>
+      <c r="D115" t="s">
+        <v>84</v>
+      </c>
+      <c r="E115" t="s">
         <v>165</v>
-      </c>
-      <c r="D115" t="s">
-        <v>165</v>
-      </c>
-      <c r="E115" t="s">
-        <v>166</v>
       </c>
       <c r="F115" t="s">
         <v>55</v>
@@ -9324,13 +9321,13 @@
         <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="D116" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="E116" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F116" t="s">
         <v>50</v>
@@ -9396,13 +9393,13 @@
         <v>112</v>
       </c>
       <c r="C117" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="D117" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="E117" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F117" t="s">
         <v>40</v>
@@ -9474,13 +9471,13 @@
         <v>113</v>
       </c>
       <c r="C118" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="D118" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="E118" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F118" t="s">
         <v>55</v>
@@ -9588,7 +9585,7 @@
     </row>
     <row r="126" spans="5:23" x14ac:dyDescent="0.25">
       <c r="E126" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O126">
         <v>69222423</v>
@@ -9605,7 +9602,7 @@
     </row>
     <row r="128" spans="5:22" x14ac:dyDescent="0.25">
       <c r="E128" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O128">
         <v>-69222423</v>
